--- a/docs/Project/EEPROM_Structure.xlsx
+++ b/docs/Project/EEPROM_Structure.xlsx
@@ -5,17 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BadBa\Marlin-bugfix-2.1.x\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BadBa\Marlin-bugfix-2.1.x\docs\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69689ACF-3188-4857-9577-33422C11DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B729AB1-24BF-4ABE-AED5-3064F9FF10E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F77794-7185-4B15-A2B1-BA8B0B7F7296}"/>
   </bookViews>
   <sheets>
     <sheet name="STRUCTURE" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">STRUCTURE!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="607">
   <si>
     <t xml:space="preserve">  /**</t>
   </si>
@@ -1780,6 +1784,72 @@
   </si>
   <si>
     <t xml:space="preserve">    // HAS_LCD_BRIGHTNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Display Sleep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Controller fan settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // POWER_LOSS_RECOVERY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // FWRETRACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // EDITABLE_HOMING_FEEDRATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // !NO_VOLUMETRIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // HAS_TRINAMIC_CONFIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // LIN_ADVANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Stepper Motors Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   //</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // CNC_COORDINATE_SYSTEMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // SKEW_CORRECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ADVANCED_PAUSE_FEATURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Tool Change Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // BACKLASH_COMPENSATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // EXTENSIBLE_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Ender-3 V2 DWIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // CASELIGHT_USES_BRIGHTNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // PASSWORD_FEATURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Ethernet settings</t>
+  </si>
+  <si>
+    <t>60.10</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1877,6 +1947,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2195,12 +2271,15 @@
   <dimension ref="A1:C1012"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="50.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="75.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>606</v>
+      </c>
       <c r="B1" s="5" t="s">
         <v>566</v>
       </c>
@@ -4756,576 +4835,723 @@
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C463" t="s">
+      <c r="B463" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C463" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C464" t="s">
+      <c r="A464" s="1">
+        <v>29</v>
+      </c>
+      <c r="B464" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="C464" s="8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="466" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B465" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C466" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="467" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C467" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="468" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" s="1">
+        <v>29.1</v>
+      </c>
       <c r="C468" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="469" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C469" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="470" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" s="1">
+        <v>29.2</v>
+      </c>
       <c r="C470" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="471" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C471" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="472" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C472" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" t="s">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B474" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C474" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>30</v>
+      </c>
+      <c r="B475" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="C475" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="477" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B476" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C476" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C477" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="478" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C478" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="479" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C479" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="480" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C480" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="481" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C481" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C482" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="483" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C483" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="484" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" s="1">
+        <v>30.1</v>
+      </c>
       <c r="C484" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="485" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C485" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" t="s">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B487" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C487" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>31</v>
+      </c>
+      <c r="B488" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C488" s="8" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="490" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B489" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C489" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C490" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="491" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C491" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="492" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C492" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="493" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C493" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="494" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" s="1">
+        <v>31.1</v>
+      </c>
       <c r="C494" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="495" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" s="1">
+        <v>31.2</v>
+      </c>
       <c r="C495" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="496" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C496" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" t="s">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B498" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" s="1">
+        <v>32</v>
+      </c>
+      <c r="B499" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="C499" s="8" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="501" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B500" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C501" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="502" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C502" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="503" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C503" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="504" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C504" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="505" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C505" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="506" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" s="1">
+        <v>32.1</v>
+      </c>
       <c r="C506" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="508" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C508" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="509" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C509" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="510" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C510" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="511" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" s="1">
+        <v>32.200000000000003</v>
+      </c>
       <c r="C511" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="512" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C512" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" t="s">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B514" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" s="1">
+        <v>33</v>
+      </c>
+      <c r="B515" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="C515" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="517" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B516" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C517" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="518" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C518" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="519" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" s="1">
+        <v>33.1</v>
+      </c>
       <c r="C519" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="520" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C520" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" t="s">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B522" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" s="1">
+        <v>34</v>
+      </c>
+      <c r="B523" s="4" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="525" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C523" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B524" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C525" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="526" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C526" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="527" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>34.1</v>
+      </c>
       <c r="C527" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="528" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C528" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" t="s">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B530" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="1">
+        <v>35</v>
+      </c>
+      <c r="B531" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C531" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="533" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B532" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C533" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="534" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C534" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="536" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C536" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="538" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="1">
+        <v>35.1</v>
+      </c>
       <c r="C538" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="539" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="1">
+        <v>35.200000000000003</v>
+      </c>
       <c r="C539" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="540" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C540" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="541" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="C541" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="542" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C542" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="543" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C543" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="544" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="C544" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="545" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C545" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="547" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C547" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="549" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C549" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="550" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="1">
+        <v>35.1</v>
+      </c>
       <c r="C550" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="551" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C551" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="552" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="1">
+        <v>35.200000000000003</v>
+      </c>
       <c r="C552" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="553" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C553" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="554" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="C554" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="556" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C556" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="557" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C557" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" t="s">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B559" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C559" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="1">
+        <v>36</v>
+      </c>
+      <c r="B560" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="C560" s="8" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="562" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B561" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="562" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C562" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="563" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C563" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="565" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C565" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="567" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C567" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="568" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C568" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="569" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C569" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="570" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C570" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="571" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C571" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="572" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C572" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="573" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C573" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="574" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C574" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="575" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C575" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="576" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C576" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="577" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C577" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="578" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C578" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="579" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C579" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="580" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C580" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="581" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C581" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="582" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C582" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="583" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C583" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="584" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C584" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="585" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C585" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="586" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C586" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="587" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C587" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="588" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C588" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="589" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C589" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="590" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C590" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="591" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" s="1">
+        <v>36.1</v>
+      </c>
       <c r="C591" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="592" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C592" t="s">
         <v>38</v>
       </c>
@@ -5480,77 +5706,83 @@
         <v>32</v>
       </c>
     </row>
-    <row r="625" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C625" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="626" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C626" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="627" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C627" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="628" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C628" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="629" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C629" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="630" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C630" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="631" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C631" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="632" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C632" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="633" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A633" s="1">
+        <v>36.200000000000003</v>
+      </c>
       <c r="C633" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="634" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C634" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" t="s">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B636" s="7"/>
+      <c r="C636" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B637" s="7"/>
+      <c r="C637" s="10" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="639" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B638" s="7"/>
+      <c r="C638" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C639" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C640" t="s">
         <v>352</v>
       </c>
@@ -5635,72 +5867,78 @@
         <v>367</v>
       </c>
     </row>
-    <row r="657" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C657" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="658" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C658" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="659" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A659" s="1">
+        <v>36.299999999999997</v>
+      </c>
       <c r="C659" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="660" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C660" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" t="s">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B662" s="7"/>
+      <c r="C662" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B663" s="7"/>
+      <c r="C663" s="10" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="665" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B664" s="7"/>
+      <c r="C664" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C665" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="666" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C666" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="668" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C668" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="669" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C669" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="670" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C670" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="671" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C671" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="672" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C672" t="s">
         <v>376</v>
       </c>
@@ -5785,1372 +6023,1833 @@
         <v>392</v>
       </c>
     </row>
-    <row r="689" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C689" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="690" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C690" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="691" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A691" s="1">
+        <v>36.4</v>
+      </c>
       <c r="C691" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="692" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C692" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" t="s">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B694" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C694" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A695" s="1">
+        <v>37</v>
+      </c>
+      <c r="B695" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C695" s="8" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="697" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B696" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C696" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C697" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="698" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C698" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="699" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C699" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="700" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A700" s="1">
+        <v>37.1</v>
+      </c>
       <c r="C700" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="701" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C701" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="702" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C702" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="703" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A703" s="1">
+        <v>37.200000000000003</v>
+      </c>
       <c r="C703" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="704" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C704" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="705" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C705" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="706" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C706" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" t="s">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B708" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C708" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A709" s="1">
+        <v>38</v>
+      </c>
+      <c r="B709" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="C709" s="8" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="711" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B710" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C710" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C711" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="712" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C712" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="714" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C714" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="715" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A715" s="1">
+        <v>38.1</v>
+      </c>
       <c r="C715" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="716" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C716" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="717" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C717" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="718" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A718" s="1">
+        <v>38.1</v>
+      </c>
       <c r="C718" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="719" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C719" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="720" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C720" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" t="s">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B722" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C722" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A723" s="1">
+        <v>39</v>
+      </c>
+      <c r="B723" s="4" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" t="s">
+      <c r="C723" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B724" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="C724" s="8" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="725" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C725" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="726" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C726" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="727" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A727" s="1">
+        <v>39.1</v>
+      </c>
       <c r="C727" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="728" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C728" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" t="s">
+    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B730" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C730" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A731" s="1">
+        <v>40</v>
+      </c>
+      <c r="B731" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C731" s="8" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="733" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B732" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C732" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C733" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="734" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C734" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="735" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C735" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="736" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C736" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="737" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C737" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="738" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A738" s="1">
+        <v>40.1</v>
+      </c>
       <c r="C738" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="739" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C739" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" t="s">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B741" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C741" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A742" s="1">
+        <v>41</v>
+      </c>
+      <c r="B742" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="C742" s="8" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="744" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B743" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C743" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C744" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="745" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C745" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="746" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A746" s="1">
+        <v>41.1</v>
+      </c>
       <c r="C746" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="747" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C747" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" t="s">
+    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B749" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C749" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A750" s="1">
+        <v>42</v>
+      </c>
+      <c r="B750" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="C750" s="8" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="752" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B751" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C751" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C752" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="753" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C753" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="754" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C754" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="755" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A755" s="1">
+        <v>42.1</v>
+      </c>
       <c r="C755" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="756" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C756" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="757" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C757" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" t="s">
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B759" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C759" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A760" s="1">
+        <v>43</v>
+      </c>
+      <c r="B760" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="C760" s="8" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="763" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B761" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C761" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C763" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="764" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C764" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="765" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A765" s="1">
+        <v>43.1</v>
+      </c>
       <c r="C765" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="766" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C766" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" t="s">
+    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B768" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C768" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A769" s="1">
+        <v>44</v>
+      </c>
+      <c r="B769" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="C769" s="8" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="771" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B770" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C770" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C771" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="772" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C772" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="773" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C773" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="774" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C774" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="775" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C775" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="776" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C776" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="777" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C777" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="778" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C778" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="779" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C779" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="780" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C780" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="781" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C781" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="782" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C782" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="783" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C783" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="784" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C784" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="785" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C785" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="786" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C786" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="787" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A787" s="1">
+        <v>44.1</v>
+      </c>
       <c r="C787" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="788" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A788" s="1">
+        <v>44.2</v>
+      </c>
       <c r="C788" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="789" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A789" s="1">
+        <v>44.3</v>
+      </c>
       <c r="C789" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="790" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C790" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="791" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C791" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="793" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C793" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="794" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C794" t="s">
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B793" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C793" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A794" s="1">
+        <v>45</v>
+      </c>
+      <c r="B794" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="C794" s="8" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="795" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C795" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="796" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B795" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C795" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C796" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="797" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C797" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="798" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C798" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="799" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C799" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="800" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C800" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="801" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A801" s="1">
+        <v>45.1</v>
+      </c>
       <c r="C801" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="802" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C802" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="803" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C803" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="805" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C805" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="806" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C806" t="s">
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B805" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C805" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A806" s="1">
+        <v>46</v>
+      </c>
+      <c r="B806" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="C806" s="8" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="807" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C807" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="808" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B807" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C807" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C808" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="809" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C809" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="810" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C810" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="811" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C811" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="812" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C812" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="813" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A813" s="1">
+        <v>46.1</v>
+      </c>
       <c r="C813" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="814" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C814" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="815" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C815" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="817" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C817" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="818" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C818" t="s">
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B817" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C817" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A818" s="1">
+        <v>47</v>
+      </c>
+      <c r="B818" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="C818" s="8" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="819" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C819" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="820" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B819" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C819" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C820" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="821" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A821" s="1">
+        <v>47.1</v>
+      </c>
       <c r="C821" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="822" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C822" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="824" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C824" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="825" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C825" t="s">
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B824" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C824" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A825" s="1">
+        <v>48</v>
+      </c>
+      <c r="B825" s="4" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="826" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C826" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="827" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C825" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B826" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C826" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C827" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="828" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A828" s="1">
+        <v>48.1</v>
+      </c>
       <c r="C828" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="829" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C829" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="831" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C831" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="832" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C832" t="s">
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B831" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C831" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A832" s="1">
+        <v>49</v>
+      </c>
+      <c r="B832" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="C832" s="8" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="833" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C833" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="834" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B833" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C833" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C834" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="835" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A835" s="1">
+        <v>49.1</v>
+      </c>
       <c r="C835" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="836" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A836" s="1">
+        <v>49.2</v>
+      </c>
       <c r="C836" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="837" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C837" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="839" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C839" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="840" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C840" t="s">
+    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B839" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C839" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A840" s="1">
+        <v>50</v>
+      </c>
+      <c r="B840" s="4" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="841" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C841" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="842" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C840" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B841" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C841" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C842" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="843" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A843" s="1">
+        <v>50.1</v>
+      </c>
       <c r="C843" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="844" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C844" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="846" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C846" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="847" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C847" t="s">
+    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B846" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C846" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A847" s="1">
+        <v>51</v>
+      </c>
+      <c r="B847" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="C847" s="8" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="848" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C848" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="849" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B848" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C848" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C849" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="850" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C850" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="851" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C851" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="852" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C852" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="853" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C853" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="854" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C854" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="855" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C855" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="856" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C856" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="857" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A857" s="1">
+        <v>51.1</v>
+      </c>
       <c r="C857" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="858" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A858" s="1">
+        <v>51.2</v>
+      </c>
       <c r="C858" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="859" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A859" s="1">
+        <v>51.3</v>
+      </c>
       <c r="C859" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="860" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A860" s="1">
+        <v>51.4</v>
+      </c>
       <c r="C860" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="861" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A861" s="1">
+        <v>51.5</v>
+      </c>
       <c r="C861" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="862" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C862" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="863" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C863" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="865" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C865" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="866" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C866" t="s">
+    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B865" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C865" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A866" s="1">
+        <v>52</v>
+      </c>
+      <c r="B866" s="4" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="867" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C867" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="868" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C866" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B867" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C867" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C868" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="869" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A869" s="1">
+        <v>52.1</v>
+      </c>
       <c r="C869" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="870" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C870" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="872" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C872" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="873" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C873" t="s">
+    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B872" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C872" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A873" s="1">
+        <v>53</v>
+      </c>
+      <c r="B873" s="4" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="874" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C874" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="875" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C873" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B874" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C874" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C875" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="876" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A876" s="1">
+        <v>53.1</v>
+      </c>
       <c r="C876" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="877" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C877" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="879" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C879" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="880" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C880" t="s">
+    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B879" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C879" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A880" s="1">
+        <v>54</v>
+      </c>
+      <c r="B880" s="4" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="881" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C881" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="882" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C880" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B881" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C881" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C882" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="883" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A883" s="1">
+        <v>54.1</v>
+      </c>
       <c r="C883" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="884" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A884" s="1">
+        <v>54.2</v>
+      </c>
       <c r="C884" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="885" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A885" s="1">
+        <v>54.3</v>
+      </c>
       <c r="C885" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="886" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A886" s="1">
+        <v>54.4</v>
+      </c>
       <c r="C886" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="887" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C887" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="889" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C889" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="890" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C890" t="s">
+    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B889" s="7"/>
+      <c r="C889" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B890" s="7"/>
+      <c r="C890" s="10" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="891" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C891" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="892" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B891" s="7"/>
+      <c r="C891" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C892" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="893" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A893" s="1">
+        <v>54.5</v>
+      </c>
       <c r="C893" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="894" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C894" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="896" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C896" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="897" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C897" t="s">
+    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B896" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C896" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A897" s="1">
+        <v>55</v>
+      </c>
+      <c r="B897" s="4" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="898" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C898" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="899" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C897" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B898" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C898" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C899" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="900" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A900" s="1">
+        <v>55.1</v>
+      </c>
       <c r="C900" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="901" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C901" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="903" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B903" t="s">
+        <v>14</v>
+      </c>
       <c r="C903" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="904" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A904" s="1">
+        <v>56</v>
+      </c>
+      <c r="B904" t="s">
+        <v>501</v>
+      </c>
       <c r="C904" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="905" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B905" t="s">
+        <v>14</v>
+      </c>
       <c r="C905" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="906" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C906" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="907" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C907" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="908" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A908" s="1">
+        <v>56.1</v>
+      </c>
       <c r="C908" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="909" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C909" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="911" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B911" t="s">
+        <v>14</v>
+      </c>
       <c r="C911" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="912" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A912" s="1">
+        <v>57</v>
+      </c>
+      <c r="B912" t="s">
+        <v>505</v>
+      </c>
       <c r="C912" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="913" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B913" t="s">
+        <v>14</v>
+      </c>
       <c r="C913" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="914" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C914" t="s">
+    <row r="914" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C914" s="8" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="915" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C915" t="s">
+    <row r="915" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C915" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="916" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C916" t="s">
+    <row r="916" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C916" s="8" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="917" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C917" t="s">
+    <row r="917" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C917" s="8" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="918" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C918" t="s">
+    <row r="918" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C918" s="8" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="919" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C919" t="s">
+    <row r="919" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C919" s="8" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="920" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C920" t="s">
+    <row r="920" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C920" s="8" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="921" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C921" t="s">
+    <row r="921" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C921" s="8" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="922" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C922" t="s">
+    <row r="922" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C922" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="923" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C923" t="s">
+    <row r="923" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C923" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="925" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C925" t="s">
+    <row r="924" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C924" s="8"/>
+    </row>
+    <row r="925" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C925" s="8" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="926" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C926" t="s">
+    <row r="926" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C926" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="927" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C927" t="s">
+    <row r="927" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C927" s="8" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="928" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C928" t="s">
+    <row r="928" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C928" s="8" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="929" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C929" t="s">
+      <c r="C929" s="8" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="930" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C930" t="s">
+      <c r="C930" s="8" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="931" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C931" t="s">
+      <c r="C931" s="8" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="932" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C932" t="s">
+      <c r="C932" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="933" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C933" t="s">
+      <c r="C933" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="934" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C934" t="s">
+      <c r="C934" s="8" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="935" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C935" s="8"/>
+    </row>
     <row r="936" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C936" t="s">
+      <c r="C936" s="8" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="937" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C937" t="s">
+      <c r="C937" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="938" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C938" t="s">
+      <c r="C938" s="8" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="939" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C939" t="s">
+      <c r="C939" s="8" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="940" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C940" t="s">
+      <c r="C940" s="8" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="941" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C941" t="s">
+      <c r="C941" s="8" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="942" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C942" t="s">
+      <c r="C942" s="8" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="943" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C943" t="s">
+      <c r="C943" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="944" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C944" t="s">
+      <c r="C944" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="945" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C945" t="s">
+    <row r="945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C945" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="947" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C947" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="948" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C948" t="s">
+    <row r="947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B947" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C947" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A948" s="1">
+        <v>58</v>
+      </c>
+      <c r="B948" s="4" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="949" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C949" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="950" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C948" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B949" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C949" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C950" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="951" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C951" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="952" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C952" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="954" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C954" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="955" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C955" t="s">
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B954" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C954" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A955" s="1">
+        <v>59</v>
+      </c>
+      <c r="B955" s="4" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="956" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C956" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="957" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C955" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B956" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C956" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C957" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="958" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A958" s="1">
+        <v>59.1</v>
+      </c>
       <c r="C958" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="959" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C959" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="961" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C961" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="962" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C962" t="s">
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B961" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C961" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A962" s="1">
+        <v>60</v>
+      </c>
+      <c r="B962" s="4" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="963" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C963" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="964" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C962" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B963" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C963" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C964" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="965" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A965" s="1">
+        <v>60.1</v>
+      </c>
       <c r="C965" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="966" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C966" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="967" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A967" s="1">
+        <v>60.2</v>
+      </c>
       <c r="C967" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="968" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A968" s="1">
+        <v>60.3</v>
+      </c>
       <c r="C968" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="969" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A969" s="1">
+        <v>60.4</v>
+      </c>
       <c r="C969" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="970" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A970" s="1">
+        <v>60.5</v>
+      </c>
       <c r="C970" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="971" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A971" s="1">
+        <v>60.6</v>
+      </c>
       <c r="C971" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="972" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A972" s="1">
+        <v>60.7</v>
+      </c>
       <c r="C972" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="973" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A973" s="1">
+        <v>60.8</v>
+      </c>
       <c r="C973" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="974" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A974" s="1">
+        <v>60.9</v>
+      </c>
       <c r="C974" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="975" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A975" s="13" t="s">
+        <v>605</v>
+      </c>
       <c r="C975" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="976" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C976" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="977" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C977" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="978" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C978" t="s">
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B977" s="15"/>
+      <c r="C977" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A978" s="1">
+        <v>61</v>
+      </c>
+      <c r="B978" s="15"/>
+      <c r="C978" s="3" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="979" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C979" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="980" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C980" t="s">
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B979" s="15"/>
+      <c r="C979" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B980" s="15"/>
+      <c r="C980" s="3" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="981" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C981" t="s">
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B981" s="15"/>
+      <c r="C981" s="3" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="982" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C982" t="s">
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B982" s="15"/>
+      <c r="C982" s="3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="983" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C983" t="s">
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A983" s="1">
+        <v>61.1</v>
+      </c>
+      <c r="B983" s="15"/>
+      <c r="C983" s="3" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="985" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C985" t="s">
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B984" s="15"/>
+      <c r="C984" s="3"/>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B985" s="15"/>
+      <c r="C985" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="986" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C986" t="s">
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B986" s="15"/>
+      <c r="C986" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="987" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C987" t="s">
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A987" s="1">
+        <v>61.2</v>
+      </c>
+      <c r="B987" s="15"/>
+      <c r="C987" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="988" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C988" t="s">
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A988" s="1">
+        <v>61.3</v>
+      </c>
+      <c r="B988" s="15"/>
+      <c r="C988" s="3" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="989" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C989" t="s">
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B989" s="15"/>
+      <c r="C989" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="990" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C990" t="s">
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B990" s="15"/>
+      <c r="C990" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="991" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C991" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="992" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C992" t="s">
         <v>546</v>
       </c>
